--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T16:11:49+00:00</t>
+    <t>2025-08-01T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T13:09:58+00:00</t>
+    <t>2025-08-04T10:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="84">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T10:11:31+00:00</t>
+    <t>2025-08-04T13:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,24 +93,24 @@
     <t>Source</t>
   </si>
   <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/DocumentEntry</t>
   </si>
   <si>
-    <t>Target</t>
+    <t/>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-comprehensive-document-reference</t>
   </si>
   <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Relationship</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>DocumentEntry.entryUUID</t>
   </si>
   <si>
@@ -126,6 +126,18 @@
     <t>DocumentReference.identifier</t>
   </si>
   <si>
+    <t>DocumentEntry.mimeType</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.contentType</t>
+  </si>
+  <si>
+    <t>DocumentEntry.availabilityStatus</t>
+  </si>
+  <si>
+    <t>related-to</t>
+  </si>
+  <si>
     <t>DocumentEntry.hash</t>
   </si>
   <si>
@@ -150,6 +162,12 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
+    <t>DocumentEntry.repositoryUniqueId</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.url</t>
+  </si>
+  <si>
     <t>DocumentEntry.serviceStartTime</t>
   </si>
   <si>
@@ -172,6 +190,9 @@
   </si>
   <si>
     <t>DocumentReference.context.sourcePatientInfo</t>
+  </si>
+  <si>
+    <t>DocumentEntry.URI</t>
   </si>
   <si>
     <t>DocumentEntry.title</t>
@@ -377,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -492,22 +513,6 @@
       </c>
       <c r="B14" s="2"/>
     </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -515,7 +520,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -523,33 +528,33 @@
         <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>28</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -597,11 +602,9 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
@@ -662,7 +665,7 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>50</v>
@@ -717,59 +720,59 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E19" s="2"/>
     </row>
@@ -782,74 +785,126 @@
         <v>33</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="E25" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E29" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T13:10:17+00:00</t>
+    <t>2026-06-10T15:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,13 +102,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/DocumentEntry</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/DocumentEntry|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-comprehensive-document-reference</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-comprehensive-document-reference|3.1.0</t>
   </si>
   <si>
     <t>DocumentEntry.entryUUID</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:39:40+00:00</t>
+    <t>2026-06-10T15:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:45:32+00:00</t>
+    <t>2026-06-10T15:59:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:59:45+00:00</t>
+    <t>2026-06-10T16:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:12:06+00:00</t>
+    <t>2026-06-10T16:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:18:52+00:00</t>
+    <t>2026-06-11T15:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:47:13+00:00</t>
+    <t>2026-06-11T15:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:59:09+00:00</t>
+    <t>2026-06-11T16:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:49:00+00:00</t>
+    <t>2026-06-12T14:52:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:52:39+00:00</t>
+    <t>2026-06-12T14:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:55:33+00:00</t>
+    <t>2026-06-12T14:56:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:56:09+00:00</t>
+    <t>2026-06-12T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:58:42+00:00</t>
+    <t>2026-06-12T15:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:04:49+00:00</t>
+    <t>2026-06-12T15:09:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:09:19+00:00</t>
+    <t>2026-06-12T15:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:31:20+00:00</t>
+    <t>2026-06-12T15:45:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:45:22+00:00</t>
+    <t>2026-06-12T16:24:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T16:24:39+00:00</t>
+    <t>2026-06-16T12:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:17:15+00:00</t>
+    <t>2026-06-16T12:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:25:33+00:00</t>
+    <t>2026-06-17T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:47:53+00:00</t>
+    <t>2026-06-17T07:58:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:58:49+00:00</t>
+    <t>2026-06-17T08:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:05:28+00:00</t>
+    <t>2026-06-17T08:38:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:38:09+00:00</t>
+    <t>2026-06-17T08:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:46:38+00:00</t>
+    <t>2026-06-17T08:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:50:19+00:00</t>
+    <t>2026-06-17T11:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:32:53+00:00</t>
+    <t>2026-06-17T11:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:35:28+00:00</t>
+    <t>2026-06-17T11:36:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/documentReferenceToPDSM.xlsx
+++ b/add-info-dmp/ig/documentReferenceToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:36:10+00:00</t>
+    <t>2026-06-17T12:12:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
